--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486519_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486519_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.348</v>
+        <v>5.2228</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3036</v>
+        <v>2.8566</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0444</v>
+        <v>2.3663</v>
       </c>
       <c r="G2" t="n">
         <v>4.4629</v>
@@ -610,13 +610,13 @@
         <v>3.0451</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3853</v>
+        <v>0.2602</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6321</v>
+        <v>0.1851</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7532</v>
+        <v>0.0751</v>
       </c>
       <c r="V2" t="n">
         <v>0.9347</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0053</v>
+        <v>4.9717</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6949</v>
+        <v>2.3222</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3104</v>
+        <v>2.6495</v>
       </c>
       <c r="G3" t="n">
         <v>0.7811</v>
@@ -688,13 +688,13 @@
         <v>3.2626</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8855</v>
+        <v>0.0808</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4554</v>
+        <v>0.1719</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4301</v>
+        <v>-0.091</v>
       </c>
       <c r="V3" t="n">
         <v>1.4997</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4835</v>
+        <v>2.6021</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6629</v>
+        <v>1.8431</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8206</v>
+        <v>0.7589</v>
       </c>
       <c r="G4" t="n">
         <v>1.0075</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1336</v>
+        <v>-0.015</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3305</v>
+        <v>-0.1502</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1968</v>
+        <v>0.1352</v>
       </c>
       <c r="V4" t="n">
         <v>0.7395</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. CAPALBO</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2824</v>
+        <v>-0.3363</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1219</v>
+        <v>-1.0564</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1605</v>
+        <v>0.7201</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8324</v>
+        <v>-2.4262</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8221</v>
+        <v>-1.3473</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0103</v>
+        <v>-1.079</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5721</v>
+        <v>-1.552</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9074</v>
+        <v>-2.1074</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6647</v>
+        <v>0.5554</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7397</v>
+        <v>-0.8742</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0854</v>
+        <v>0.7601</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6543</v>
+        <v>-1.6344</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.305</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9151</v>
+        <v>-3.2626</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6101</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5154</v>
+        <v>0.2448</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2211</v>
+        <v>0.173</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2943</v>
+        <v>0.0718</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3252</v>
+        <v>3.5851</v>
       </c>
       <c r="W5" t="n">
+        <v>3.5851</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.3252</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3163</v>
+        <v>-0.7698</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9343</v>
+        <v>1.3575</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2506</v>
+        <v>-2.1273</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3063</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5773</v>
+        <v>0.1238</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5997</v>
+        <v>0.0228</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0224</v>
+        <v>0.1009</v>
       </c>
       <c r="V6" t="n">
         <v>0.1952</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>L. CAPALBO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6001</v>
+        <v>-0.7765</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7794</v>
+        <v>-0.2769</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1793</v>
+        <v>-0.4996</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4311</v>
+        <v>1.8324</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9275</v>
+        <v>1.8221</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3587</v>
+        <v>0.0103</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4911</v>
+        <v>3.5721</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8974</v>
+        <v>1.9074</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5937</v>
+        <v>1.6647</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9222</v>
+        <v>-1.7397</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0302</v>
+        <v>-0.0854</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9523</v>
+        <v>-1.6543</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.7401</v>
+        <v>-3.9151</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8276</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0034</v>
+        <v>0.0213</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2091</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7943</v>
+        <v>-0.0448</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.2599</v>
+        <v>-1.3252</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5204</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.321</v>
+        <v>-1.0796</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6404</v>
+        <v>-0.6424</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3194</v>
+        <v>-0.4372</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4262</v>
+        <v>-0.4311</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3473</v>
+        <v>0.9275</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.079</v>
+        <v>-1.3587</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.552</v>
+        <v>1.4911</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.1074</v>
+        <v>0.8974</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5554</v>
+        <v>0.5937</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8742</v>
+        <v>-1.9222</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7601</v>
+        <v>0.0302</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6344</v>
+        <v>-1.9523</v>
       </c>
       <c r="P8" t="n">
+        <v>1.0875</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.7401</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>2.8276</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7399</v>
+        <v>0.5239</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.411</v>
+        <v>0.3461</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3289</v>
+        <v>0.1778</v>
       </c>
       <c r="V8" t="n">
-        <v>3.5851</v>
+        <v>-2.2599</v>
       </c>
       <c r="W8" t="n">
-        <v>3.5851</v>
+        <v>-0.7395</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5161</v>
+        <v>-2.3252</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2252</v>
+        <v>0.1387</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7413</v>
+        <v>-2.4639</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8144</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.202</v>
+        <v>-0.0111</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0601</v>
+        <v>-0.0264</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2621</v>
+        <v>0.0153</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9347</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7874</v>
+        <v>-2.8403</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2904</v>
+        <v>-2.7748</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.497</v>
+        <v>-0.0655</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2269</v>
@@ -1234,13 +1234,13 @@
         <v>2.8276</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6458</v>
+        <v>-0.6988</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5924</v>
+        <v>-0.0769</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0534</v>
+        <v>-0.6219</v>
       </c>
       <c r="V10" t="n">
         <v>0.3904</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3559</v>
+        <v>-6.9839</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4442</v>
+        <v>-6.1955</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9117</v>
+        <v>-0.7884</v>
       </c>
       <c r="G11" t="n">
         <v>-3.261</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3973</v>
+        <v>-0.0252</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4795</v>
+        <v>-0.2307</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0822</v>
+        <v>0.2055</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.342399999999999</v>
+        <v>-2.314999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4554</v>
+        <v>-2.4279</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1130000000000002</v>
+        <v>0.1129000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.382000000000001</v>
+        <v>-2.382</v>
       </c>
       <c r="H12" t="n">
         <v>12.2723</v>
@@ -1390,13 +1390,13 @@
         <v>19.5755</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5226999999999997</v>
+        <v>0.5046999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5467000000000002</v>
+        <v>0.4808</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0239000000000002</v>
+        <v>0.0239</v>
       </c>
       <c r="V12" t="n">
         <v>2.8248</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5291</v>
+        <v>4.8143</v>
       </c>
       <c r="E13" t="n">
-        <v>4.116</v>
+        <v>4.3395</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4131</v>
+        <v>0.4748</v>
       </c>
       <c r="G13" t="n">
         <v>1.1182</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.3263</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7294</v>
+        <v>-0.5059</v>
       </c>
       <c r="U13" t="n">
-        <v>0.118</v>
+        <v>0.1796</v>
       </c>
       <c r="V13" t="n">
         <v>2.0647</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1346</v>
+        <v>3.3941</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8768</v>
+        <v>1.6533</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2579</v>
+        <v>1.7408</v>
       </c>
       <c r="G14" t="n">
         <v>1.2759</v>
@@ -1546,13 +1546,13 @@
         <v>3.2626</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0534</v>
+        <v>1.3129</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.6742</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1557</v>
+        <v>0.6387</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9347</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7776</v>
+        <v>3.2876</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2794</v>
+        <v>1.6147</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4981</v>
+        <v>1.6729</v>
       </c>
       <c r="G15" t="n">
         <v>0.2736</v>
@@ -1624,13 +1624,13 @@
         <v>3.9151</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5018</v>
+        <v>1.0118</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0156</v>
+        <v>0.3509</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4862</v>
+        <v>0.6609</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3904</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1275</v>
+        <v>0.6685</v>
       </c>
       <c r="E16" t="n">
-        <v>0.753</v>
+        <v>-0.2693</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3744</v>
+        <v>0.9378</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1504</v>
+        <v>0.5064</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7847</v>
+        <v>0.3558</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6343</v>
+        <v>0.1506</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4137</v>
+        <v>1.3927</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4121</v>
+        <v>0.9886</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0016</v>
+        <v>0.404</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2633</v>
+        <v>-0.8863</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6274</v>
+        <v>-0.6328</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6359</v>
+        <v>-0.2534</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.6101</v>
+        <v>-1.305</v>
       </c>
       <c r="R16" t="n">
-        <v>3.0451</v>
+        <v>2.6101</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2163</v>
+        <v>-0.3827</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4937</v>
+        <v>-0.3569</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7226</v>
+        <v>-0.0258</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.6743</v>
+        <v>-0.7602</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5581</v>
+        <v>0.2784</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0457</v>
+        <v>-0.0293</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6038</v>
+        <v>0.3077</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5064</v>
+        <v>0.1504</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3558</v>
+        <v>0.7847</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1506</v>
+        <v>-0.6343</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3927</v>
+        <v>2.4137</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9886</v>
+        <v>2.4121</v>
       </c>
       <c r="L17" t="n">
-        <v>0.404</v>
+        <v>0.0016</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8863</v>
+        <v>-2.2633</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6328</v>
+        <v>-1.6274</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2534</v>
+        <v>-0.6359</v>
       </c>
       <c r="P17" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-2.6101</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6101</v>
+        <v>3.0451</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4932</v>
+        <v>1.3672</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1334</v>
+        <v>0.7114</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3598</v>
+        <v>0.6558</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7602</v>
+        <v>-1.6743</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2074</v>
+        <v>-0.1264</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0735</v>
+        <v>1.1853</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2809</v>
+        <v>-1.3117</v>
       </c>
       <c r="G18" t="n">
         <v>2.8545</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0396</v>
+        <v>-0.9587</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5732</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3546</v>
+        <v>-0.3854</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9347</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2161</v>
+        <v>-0.6374</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8286</v>
+        <v>-2.2757</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6125</v>
+        <v>1.6383</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8327</v>
@@ -1936,13 +1936,13 @@
         <v>2.6101</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4644</v>
+        <v>1.0431</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0227</v>
+        <v>0.5756</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4417</v>
+        <v>0.4675</v>
       </c>
       <c r="V19" t="n">
         <v>0.9347</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.548</v>
+        <v>-1.4055</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9016</v>
+        <v>-1.7899</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3536</v>
+        <v>0.3844</v>
       </c>
       <c r="G20" t="n">
         <v>0.5945</v>
@@ -2014,13 +2014,13 @@
         <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1849</v>
+        <v>-0.0424</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>J. LOPEZ SANTANA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4034</v>
+        <v>-2.0826</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6044</v>
+        <v>-2.0489</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.0337</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6394</v>
+        <v>-0.9194</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0347</v>
+        <v>-2.8255</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3953</v>
+        <v>1.9061</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0201</v>
+        <v>1.7448</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4354</v>
+        <v>-1.0307</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4152</v>
+        <v>2.7755</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6193</v>
+        <v>-2.6642</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5994</v>
+        <v>-1.7948</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0199</v>
+        <v>-0.8694</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0875</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-3.4801</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>2.8276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5464</v>
+        <v>-0.5107</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6044</v>
+        <v>-0.3136</v>
       </c>
       <c r="U21" t="n">
-        <v>0.058</v>
+        <v>-0.1971</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANTANA</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4095</v>
+        <v>-3.3583</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8313</v>
+        <v>-2.4927</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5783</v>
+        <v>-0.8657</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9194</v>
+        <v>-0.6394</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.8255</v>
+        <v>-2.0347</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9061</v>
+        <v>1.3953</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7448</v>
+        <v>-0.0201</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0307</v>
+        <v>-1.4354</v>
       </c>
       <c r="L22" t="n">
-        <v>2.7755</v>
+        <v>1.4152</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6642</v>
+        <v>-0.6193</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7948</v>
+        <v>-0.5994</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8694</v>
+        <v>-0.0199</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4801</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8276</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8376</v>
+        <v>-0.5014</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0959</v>
+        <v>-0.4927</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7417</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.342500000000001</v>
+        <v>4.832700000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1129000000000002</v>
+        <v>-0.113</v>
       </c>
       <c r="F23" t="n">
-        <v>3.4553</v>
+        <v>4.9456</v>
       </c>
       <c r="G23" t="n">
         <v>2.382</v>
@@ -2248,13 +2248,13 @@
         <v>22.8382</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5227999999999995</v>
+        <v>2.0128</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.02390000000000025</v>
+        <v>-0.02390000000000003</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5466000000000002</v>
+        <v>2.0369</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8249</v>
